--- a/uat_irt/UAT_IRT_RTSM_Workbook.xlsx
+++ b/uat_irt/UAT_IRT_RTSM_Workbook.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="244">
   <si>
     <t xml:space="preserve">IRT / RTSM User Acceptance Testing  —  how to run this UAT (parallel-group study)</t>
   </si>
@@ -88,6 +88,15 @@
   </si>
   <si>
     <t xml:space="preserve">The gate flips from NOT ready to READY only when ALL THREE are true: (1) every Critical test is Pass; (2) zero OPEN Critical or Major defects; (3) 100% requirement traceability. The gate packages evidence — it does not grant approval. A named human still reviews and signs. In the delivered workbook the gate reads NOT ready because no tests are executed yet; it turns READY as you pass them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How this connects to your real systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• UAT runs in the IRT/RTSM vendor's staging environment (a separate instance from production), loaded with a TEST randomization list, never the production list.
+• You operate the vendor's system in a browser (register a test participant, randomize, dispense, trigger resupply, invoke emergency unblinding) and reconcile what it did against your list and specs.
+• This workbook is your independent record and sign-off, not a live connection: you transcribe Status, defects, and traceability here, with dated screenshots and system exports as the evidence.
+• The signed go-live summary (gate READY plus named human signatures) is what authorizes the vendor to promote the validated build to production; the whole package is filed to the eTMF.</t>
   </si>
   <si>
     <t xml:space="preserve">100% synthetic test data. No PHI. 'Participant', not 'subject' (CDISC USUBJID/SUBJID preserved). Full worked detail: the 'UAT guide' HTML next to this file.</t>
@@ -977,7 +986,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -986,43 +995,39 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1343,7 +1348,7 @@
     <tabColor rgb="FF1F3864"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -1356,7 +1361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4"/>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -1368,8 +1373,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7"/>
+    <row r="4" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4"/>
       <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
@@ -1380,8 +1385,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7"/>
+    <row r="6" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4"/>
       <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
@@ -1392,64 +1397,64 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="n">
+    <row r="8" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="n">
+    <row r="9" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="n">
         <v>2</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="n">
         <v>3</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="n">
+    <row r="11" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="n">
         <v>4</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="n">
+    <row r="12" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="n">
         <v>5</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="n">
+    <row r="13" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="n">
         <v>6</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="n">
         <v>7</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="n">
+    <row r="15" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="n">
         <v>8</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -1457,40 +1462,51 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9" t="s">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="10" t="s">
+    <row r="17" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="10" t="s">
+    <row r="18" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="10" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="5" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9" t="s">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="10" t="s">
+    <row r="21" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="11" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="97" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1512,143 +1528,143 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
+      <c r="A1" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
+      <c r="A2" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+      <c r="B3" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="C3" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="14" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+      <c r="B4" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="14" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B5" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C5" s="13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="12" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
+      <c r="B6" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="C6" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="14" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="12" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
+      <c r="B7" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="C7" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="14" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="12" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
+      <c r="B8" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="C8" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="14" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="12" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
+      <c r="B9" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="C9" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="14" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="12" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
+      <c r="B10" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="C10" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="14" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="12" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
+      <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="C11" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="14" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="12" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
+      <c r="B12" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="C12" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="14" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="12" t="s">
         <v>55</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1690,845 +1706,845 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
+      <c r="A1" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
     </row>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="16" t="s">
+      <c r="B2" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="F2" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="G2" s="16" t="s">
+      <c r="C2" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="D2" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="F2" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="H2" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="I2" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="L2" s="16" t="s">
+      <c r="J2" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="K2" s="15" t="s">
         <v>67</v>
       </c>
+      <c r="L2" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" s="17" t="s">
+      <c r="A3" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="17" t="s">
+      <c r="B3" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="C3" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="D3" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18"/>
-      <c r="M3" s="18"/>
+      <c r="F3" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="17" t="s">
+      <c r="A4" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="B4" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="D4" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
+      <c r="F4" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="D5" s="17" t="s">
+      <c r="A5" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="B5" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="D5" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="E5" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
-      <c r="L5" s="18"/>
-      <c r="M5" s="18"/>
+      <c r="F5" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E6" s="17" t="s">
+      <c r="A6" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="B6" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="D6" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
+      <c r="F6" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="17" t="s">
+      <c r="A7" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="B7" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="D7" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="18"/>
-      <c r="L7" s="18"/>
-      <c r="M7" s="18"/>
+      <c r="F7" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="17" t="s">
+      <c r="A8" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="B8" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="D8" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="18"/>
-      <c r="L8" s="18"/>
-      <c r="M8" s="18"/>
+      <c r="F8" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E9" s="17" t="s">
+      <c r="A9" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="B9" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="G9" s="17" t="s">
+      <c r="D9" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="18"/>
+      <c r="F9" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="C10" s="17" t="s">
+      <c r="A10" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="B10" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="C10" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="D10" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="G10" s="17" t="s">
+      <c r="E10" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="18"/>
-      <c r="M10" s="18"/>
+      <c r="F10" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E11" s="17" t="s">
+      <c r="A11" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="B11" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="G11" s="17" t="s">
+      <c r="D11" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="18"/>
-      <c r="M11" s="18"/>
+      <c r="F11" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="D12" s="17" t="s">
+      <c r="A12" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="B12" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="E12" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="F12" s="17" t="s">
+      <c r="C12" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="G12" s="17" t="s">
+      <c r="D12" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="E12" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="18"/>
-      <c r="L12" s="18"/>
-      <c r="M12" s="18"/>
+      <c r="F12" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E13" s="17" t="s">
+      <c r="A13" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="F13" s="17" t="s">
+      <c r="B13" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="G13" s="17" t="s">
+      <c r="D13" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="18"/>
-      <c r="L13" s="18"/>
-      <c r="M13" s="18"/>
+      <c r="F13" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="C14" s="17" t="s">
+      <c r="A14" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="D14" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="17" t="s">
+      <c r="B14" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="C14" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="G14" s="17" t="s">
+      <c r="D14" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
-      <c r="L14" s="18"/>
-      <c r="M14" s="18"/>
+      <c r="F14" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E15" s="17" t="s">
+      <c r="A15" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="F15" s="17" t="s">
+      <c r="B15" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C15" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="G15" s="17" t="s">
+      <c r="D15" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="18"/>
-      <c r="L15" s="18"/>
-      <c r="M15" s="18"/>
+      <c r="F15" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="E16" s="17" t="s">
+      <c r="A16" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="F16" s="17" t="s">
+      <c r="B16" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="G16" s="17" t="s">
+      <c r="D16" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="E16" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="18"/>
-      <c r="L16" s="18"/>
-      <c r="M16" s="18"/>
+      <c r="F16" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E17" s="17" t="s">
+      <c r="A17" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="F17" s="17" t="s">
+      <c r="B17" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C17" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="G17" s="17" t="s">
+      <c r="D17" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="18"/>
-      <c r="L17" s="18"/>
-      <c r="M17" s="18"/>
+      <c r="F17" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" s="17" t="s">
+      <c r="A18" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="F18" s="17" t="s">
+      <c r="B18" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C18" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="G18" s="17" t="s">
+      <c r="D18" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="18"/>
-      <c r="M18" s="18"/>
+      <c r="F18" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="17"/>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="C19" s="17" t="s">
+      <c r="A19" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="D19" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E19" s="17" t="s">
+      <c r="B19" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="F19" s="17" t="s">
+      <c r="C19" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="G19" s="17" t="s">
+      <c r="D19" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="18"/>
-      <c r="K19" s="18"/>
-      <c r="L19" s="18"/>
-      <c r="M19" s="18"/>
+      <c r="F19" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="17"/>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="17" t="s">
+      <c r="A20" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="F20" s="17" t="s">
+      <c r="B20" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="C20" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="G20" s="17" t="s">
+      <c r="D20" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="18"/>
-      <c r="K20" s="18"/>
-      <c r="L20" s="18"/>
-      <c r="M20" s="18"/>
+      <c r="F20" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E21" s="17" t="s">
+      <c r="A21" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="F21" s="17" t="s">
+      <c r="B21" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="C21" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="G21" s="17" t="s">
+      <c r="D21" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="18"/>
-      <c r="K21" s="18"/>
-      <c r="L21" s="18"/>
-      <c r="M21" s="18"/>
+      <c r="F21" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="17"/>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="E22" s="17" t="s">
+      <c r="A22" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="F22" s="17" t="s">
+      <c r="B22" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="C22" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="G22" s="17" t="s">
+      <c r="D22" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="E22" s="16" t="s">
         <v>173</v>
       </c>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="18"/>
-      <c r="K22" s="18"/>
-      <c r="L22" s="18"/>
-      <c r="M22" s="18"/>
+      <c r="F22" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="C23" s="17" t="s">
+      <c r="A23" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="D23" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23" s="17" t="s">
+      <c r="B23" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="F23" s="17" t="s">
+      <c r="C23" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="G23" s="17" t="s">
+      <c r="D23" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="18"/>
-      <c r="K23" s="18"/>
-      <c r="L23" s="18"/>
-      <c r="M23" s="18"/>
+      <c r="F23" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="17"/>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="D24" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E24" s="17" t="s">
+      <c r="A24" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="B24" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="C24" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="G24" s="17" t="s">
+      <c r="D24" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="E24" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="18"/>
-      <c r="K24" s="18"/>
-      <c r="L24" s="18"/>
-      <c r="M24" s="18"/>
+      <c r="F24" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="17"/>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E25" s="17" t="s">
+      <c r="A25" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="F25" s="17" t="s">
+      <c r="B25" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="C25" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="G25" s="17" t="s">
+      <c r="D25" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E25" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="18"/>
-      <c r="K25" s="18"/>
-      <c r="L25" s="18"/>
-      <c r="M25" s="18"/>
+      <c r="F25" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="17" t="s">
-        <v>190</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="C26" s="17" t="s">
+      <c r="A26" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="D26" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="E26" s="17" t="s">
+      <c r="B26" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="F26" s="17" t="s">
+      <c r="C26" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="G26" s="17" t="s">
+      <c r="D26" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="E26" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="18"/>
-      <c r="K26" s="18"/>
-      <c r="L26" s="18"/>
-      <c r="M26" s="18"/>
+      <c r="F26" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="17"/>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="E27" s="17" t="s">
+      <c r="A27" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="F27" s="17" t="s">
+      <c r="B27" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="C27" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="G27" s="17" t="s">
+      <c r="D27" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="E27" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
-      <c r="J27" s="18"/>
-      <c r="K27" s="18"/>
-      <c r="L27" s="18"/>
-      <c r="M27" s="18"/>
+      <c r="F27" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="G27" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="17"/>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="C28" s="17" t="s">
+      <c r="A28" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="D28" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E28" s="17" t="s">
+      <c r="B28" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="F28" s="17" t="s">
+      <c r="C28" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="G28" s="17" t="s">
+      <c r="D28" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E28" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
-      <c r="J28" s="18"/>
-      <c r="K28" s="18"/>
-      <c r="L28" s="18"/>
-      <c r="M28" s="18"/>
+      <c r="F28" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="G28" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17"/>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="17" t="s">
-        <v>207</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="C29" s="17" t="s">
-        <v>208</v>
-      </c>
-      <c r="D29" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E29" s="17" t="s">
+      <c r="A29" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="F29" s="17" t="s">
+      <c r="B29" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="C29" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="G29" s="17" t="s">
+      <c r="D29" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E29" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="H29" s="18"/>
-      <c r="I29" s="18"/>
-      <c r="J29" s="18"/>
-      <c r="K29" s="18"/>
-      <c r="L29" s="18"/>
-      <c r="M29" s="18"/>
+      <c r="F29" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2570,455 +2586,455 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
+      <c r="A1" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
     </row>
     <row r="2" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="D2" s="16" t="s">
+      <c r="A2" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="15" t="s">
         <v>215</v>
       </c>
+      <c r="C2" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="C3" s="20" t="n">
+      <c r="A3" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!$C$3:$C$60,A3)</f>
         <v>1</v>
       </c>
-      <c r="D3" s="20" t="str">
+      <c r="D3" s="19" t="str">
         <f aca="false">IF(C3&gt;0,"Y","N (GAP)")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="C4" s="20" t="n">
+      <c r="A4" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!$C$3:$C$60,A4)</f>
         <v>1</v>
       </c>
-      <c r="D4" s="20" t="str">
+      <c r="D4" s="19" t="str">
         <f aca="false">IF(C4&gt;0,"Y","N (GAP)")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="20" t="n">
+      <c r="A5" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!$C$3:$C$60,A5)</f>
         <v>1</v>
       </c>
-      <c r="D5" s="20" t="str">
+      <c r="D5" s="19" t="str">
         <f aca="false">IF(C5&gt;0,"Y","N (GAP)")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="C6" s="20" t="n">
+      <c r="A6" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!$C$3:$C$60,A6)</f>
         <v>1</v>
       </c>
-      <c r="D6" s="20" t="str">
+      <c r="D6" s="19" t="str">
         <f aca="false">IF(C6&gt;0,"Y","N (GAP)")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="C7" s="20" t="n">
+      <c r="A7" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="C7" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!$C$3:$C$60,A7)</f>
         <v>1</v>
       </c>
-      <c r="D7" s="20" t="str">
+      <c r="D7" s="19" t="str">
         <f aca="false">IF(C7&gt;0,"Y","N (GAP)")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="B8" s="17" t="s">
+      <c r="A8" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="B8" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!$C$3:$C$60,A8)</f>
         <v>1</v>
       </c>
-      <c r="D8" s="20" t="str">
+      <c r="D8" s="19" t="str">
         <f aca="false">IF(C8&gt;0,"Y","N (GAP)")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="C9" s="20" t="n">
+      <c r="A9" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!$C$3:$C$60,A9)</f>
         <v>1</v>
       </c>
-      <c r="D9" s="20" t="str">
+      <c r="D9" s="19" t="str">
         <f aca="false">IF(C9&gt;0,"Y","N (GAP)")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="C10" s="20" t="n">
+      <c r="A10" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!$C$3:$C$60,A10)</f>
         <v>1</v>
       </c>
-      <c r="D10" s="20" t="str">
+      <c r="D10" s="19" t="str">
         <f aca="false">IF(C10&gt;0,"Y","N (GAP)")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="C11" s="20" t="n">
+      <c r="A11" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="C11" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!$C$3:$C$60,A11)</f>
         <v>1</v>
       </c>
-      <c r="D11" s="20" t="str">
+      <c r="D11" s="19" t="str">
         <f aca="false">IF(C11&gt;0,"Y","N (GAP)")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="C12" s="20" t="n">
+      <c r="A12" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="C12" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!$C$3:$C$60,A12)</f>
         <v>1</v>
       </c>
-      <c r="D12" s="20" t="str">
+      <c r="D12" s="19" t="str">
         <f aca="false">IF(C12&gt;0,"Y","N (GAP)")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
-        <v>208</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>209</v>
-      </c>
-      <c r="C13" s="20" t="n">
+      <c r="A13" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="C13" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!$C$3:$C$60,A13)</f>
         <v>1</v>
       </c>
-      <c r="D13" s="20" t="str">
+      <c r="D13" s="19" t="str">
         <f aca="false">IF(C13&gt;0,"Y","N (GAP)")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="C14" s="20" t="n">
+      <c r="A14" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="C14" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!$C$3:$C$60,A14)</f>
         <v>1</v>
       </c>
-      <c r="D14" s="20" t="str">
+      <c r="D14" s="19" t="str">
         <f aca="false">IF(C14&gt;0,"Y","N (GAP)")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
-        <v>197</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>198</v>
-      </c>
-      <c r="C15" s="20" t="n">
+      <c r="A15" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="C15" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!$C$3:$C$60,A15)</f>
         <v>1</v>
       </c>
-      <c r="D15" s="20" t="str">
+      <c r="D15" s="19" t="str">
         <f aca="false">IF(C15&gt;0,"Y","N (GAP)")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="20" t="n">
+      <c r="A16" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!$C$3:$C$60,A16)</f>
         <v>1</v>
       </c>
-      <c r="D16" s="20" t="str">
+      <c r="D16" s="19" t="str">
         <f aca="false">IF(C16&gt;0,"Y","N (GAP)")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" s="20" t="n">
+      <c r="A17" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!$C$3:$C$60,A17)</f>
         <v>1</v>
       </c>
-      <c r="D17" s="20" t="str">
+      <c r="D17" s="19" t="str">
         <f aca="false">IF(C17&gt;0,"Y","N (GAP)")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="B18" s="17" t="s">
+      <c r="A18" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="C18" s="20" t="n">
+      <c r="B18" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!$C$3:$C$60,A18)</f>
         <v>1</v>
       </c>
-      <c r="D18" s="20" t="str">
+      <c r="D18" s="19" t="str">
         <f aca="false">IF(C18&gt;0,"Y","N (GAP)")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="C19" s="20" t="n">
+      <c r="A19" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!$C$3:$C$60,A19)</f>
         <v>1</v>
       </c>
-      <c r="D19" s="20" t="str">
+      <c r="D19" s="19" t="str">
         <f aca="false">IF(C19&gt;0,"Y","N (GAP)")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="C20" s="20" t="n">
+      <c r="A20" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!$C$3:$C$60,A20)</f>
         <v>1</v>
       </c>
-      <c r="D20" s="20" t="str">
+      <c r="D20" s="19" t="str">
         <f aca="false">IF(C20&gt;0,"Y","N (GAP)")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="C21" s="20" t="n">
+      <c r="A21" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!$C$3:$C$60,A21)</f>
         <v>1</v>
       </c>
-      <c r="D21" s="20" t="str">
+      <c r="D21" s="19" t="str">
         <f aca="false">IF(C21&gt;0,"Y","N (GAP)")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="C22" s="20" t="n">
+      <c r="A22" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!$C$3:$C$60,A22)</f>
         <v>1</v>
       </c>
-      <c r="D22" s="20" t="str">
+      <c r="D22" s="19" t="str">
         <f aca="false">IF(C22&gt;0,"Y","N (GAP)")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="C23" s="20" t="n">
+      <c r="A23" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="C23" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!$C$3:$C$60,A23)</f>
         <v>1</v>
       </c>
-      <c r="D23" s="20" t="str">
+      <c r="D23" s="19" t="str">
         <f aca="false">IF(C23&gt;0,"Y","N (GAP)")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="C24" s="20" t="n">
+      <c r="A24" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="C24" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!$C$3:$C$60,A24)</f>
         <v>1</v>
       </c>
-      <c r="D24" s="20" t="str">
+      <c r="D24" s="19" t="str">
         <f aca="false">IF(C24&gt;0,"Y","N (GAP)")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="C25" s="20" t="n">
+      <c r="A25" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="C25" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!$C$3:$C$60,A25)</f>
         <v>1</v>
       </c>
-      <c r="D25" s="20" t="str">
+      <c r="D25" s="19" t="str">
         <f aca="false">IF(C25&gt;0,"Y","N (GAP)")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="C26" s="20" t="n">
+      <c r="A26" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="C26" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!$C$3:$C$60,A26)</f>
         <v>1</v>
       </c>
-      <c r="D26" s="20" t="str">
+      <c r="D26" s="19" t="str">
         <f aca="false">IF(C26&gt;0,"Y","N (GAP)")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="C27" s="20" t="n">
+      <c r="A27" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="C27" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!$C$3:$C$60,A27)</f>
         <v>1</v>
       </c>
-      <c r="D27" s="20" t="str">
+      <c r="D27" s="19" t="str">
         <f aca="false">IF(C27&gt;0,"Y","N (GAP)")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="C28" s="20" t="n">
+      <c r="A28" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="C28" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!$C$3:$C$60,A28)</f>
         <v>1</v>
       </c>
-      <c r="D28" s="20" t="str">
+      <c r="D28" s="19" t="str">
         <f aca="false">IF(C28&gt;0,"Y","N (GAP)")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="C29" s="20" t="n">
+      <c r="A29" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="C29" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!$C$3:$C$60,A29)</f>
         <v>1</v>
       </c>
-      <c r="D29" s="20" t="str">
+      <c r="D29" s="19" t="str">
         <f aca="false">IF(C29&gt;0,"Y","N (GAP)")</f>
         <v>Y</v>
       </c>
@@ -3056,560 +3072,560 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="15" t="s">
-        <v>216</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="A1" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="E2" s="16" t="s">
+      <c r="A2" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="C2" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="E2" s="15" t="s">
         <v>221</v>
       </c>
+      <c r="F2" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
+      <c r="A3" s="20"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
+      <c r="A4" s="20"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
+      <c r="A6" s="20"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
+      <c r="A7" s="20"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
+      <c r="A8" s="20"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
+      <c r="A13" s="20"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="21"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
+      <c r="A16" s="20"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="21"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="21"/>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="21"/>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21"/>
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
+      <c r="A20" s="20"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="21"/>
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
+      <c r="A21" s="20"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="21"/>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="21"/>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
+      <c r="A23" s="20"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="21"/>
-      <c r="B24" s="21"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
+      <c r="A24" s="20"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="21"/>
-      <c r="B25" s="21"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
+      <c r="A25" s="20"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="21"/>
-      <c r="B26" s="21"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
+      <c r="A26" s="20"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="21"/>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
+      <c r="A27" s="20"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="21"/>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
+      <c r="A28" s="20"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="21"/>
-      <c r="B29" s="21"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
+      <c r="A29" s="20"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="21"/>
-      <c r="B30" s="21"/>
-      <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
+      <c r="A30" s="20"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="21"/>
-      <c r="B31" s="21"/>
-      <c r="C31" s="21"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="21"/>
+      <c r="A31" s="20"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="21"/>
-      <c r="B32" s="21"/>
-      <c r="C32" s="21"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="21"/>
+      <c r="A32" s="20"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="21"/>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
+      <c r="A33" s="20"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="21"/>
-      <c r="B34" s="21"/>
-      <c r="C34" s="21"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
-      <c r="G34" s="21"/>
+      <c r="A34" s="20"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="21"/>
-      <c r="B35" s="21"/>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="21"/>
+      <c r="A35" s="20"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="21"/>
-      <c r="B36" s="21"/>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="21"/>
+      <c r="A36" s="20"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="21"/>
-      <c r="B37" s="21"/>
-      <c r="C37" s="21"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
-      <c r="G37" s="21"/>
+      <c r="A37" s="20"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="21"/>
-      <c r="B38" s="21"/>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="21"/>
+      <c r="A38" s="20"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="21"/>
-      <c r="B39" s="21"/>
-      <c r="C39" s="21"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21"/>
-      <c r="G39" s="21"/>
+      <c r="A39" s="20"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="20"/>
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="21"/>
-      <c r="B40" s="21"/>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21"/>
-      <c r="G40" s="21"/>
+      <c r="A40" s="20"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="21"/>
-      <c r="B41" s="21"/>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="21"/>
-      <c r="G41" s="21"/>
+      <c r="A41" s="20"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="20"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="20"/>
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="21"/>
-      <c r="B42" s="21"/>
-      <c r="C42" s="21"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="21"/>
-      <c r="G42" s="21"/>
+      <c r="A42" s="20"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="21"/>
-      <c r="B43" s="21"/>
-      <c r="C43" s="21"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="21"/>
-      <c r="G43" s="21"/>
+      <c r="A43" s="20"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="21"/>
-      <c r="B44" s="21"/>
-      <c r="C44" s="21"/>
-      <c r="D44" s="21"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="21"/>
-      <c r="G44" s="21"/>
+      <c r="A44" s="20"/>
+      <c r="B44" s="20"/>
+      <c r="C44" s="20"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="20"/>
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="21"/>
-      <c r="B45" s="21"/>
-      <c r="C45" s="21"/>
-      <c r="D45" s="21"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="21"/>
-      <c r="G45" s="21"/>
+      <c r="A45" s="20"/>
+      <c r="B45" s="20"/>
+      <c r="C45" s="20"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="21"/>
-      <c r="B46" s="21"/>
-      <c r="C46" s="21"/>
-      <c r="D46" s="21"/>
-      <c r="E46" s="21"/>
-      <c r="F46" s="21"/>
-      <c r="G46" s="21"/>
+      <c r="A46" s="20"/>
+      <c r="B46" s="20"/>
+      <c r="C46" s="20"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
     </row>
     <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="21"/>
-      <c r="B47" s="21"/>
-      <c r="C47" s="21"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="21"/>
-      <c r="G47" s="21"/>
+      <c r="A47" s="20"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="21"/>
-      <c r="B48" s="21"/>
-      <c r="C48" s="21"/>
-      <c r="D48" s="21"/>
-      <c r="E48" s="21"/>
-      <c r="F48" s="21"/>
-      <c r="G48" s="21"/>
+      <c r="A48" s="20"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20"/>
     </row>
     <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="21"/>
-      <c r="B49" s="21"/>
-      <c r="C49" s="21"/>
-      <c r="D49" s="21"/>
-      <c r="E49" s="21"/>
-      <c r="F49" s="21"/>
-      <c r="G49" s="21"/>
+      <c r="A49" s="20"/>
+      <c r="B49" s="20"/>
+      <c r="C49" s="20"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="20"/>
+      <c r="G49" s="20"/>
     </row>
     <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="21"/>
-      <c r="B50" s="21"/>
-      <c r="C50" s="21"/>
-      <c r="D50" s="21"/>
-      <c r="E50" s="21"/>
-      <c r="F50" s="21"/>
-      <c r="G50" s="21"/>
+      <c r="A50" s="20"/>
+      <c r="B50" s="20"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
     </row>
     <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="21"/>
-      <c r="B51" s="21"/>
-      <c r="C51" s="21"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="21"/>
-      <c r="G51" s="21"/>
+      <c r="A51" s="20"/>
+      <c r="B51" s="20"/>
+      <c r="C51" s="20"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="20"/>
     </row>
     <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="21"/>
-      <c r="B52" s="21"/>
-      <c r="C52" s="21"/>
-      <c r="D52" s="21"/>
-      <c r="E52" s="21"/>
-      <c r="F52" s="21"/>
-      <c r="G52" s="21"/>
+      <c r="A52" s="20"/>
+      <c r="B52" s="20"/>
+      <c r="C52" s="20"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
     </row>
     <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="21"/>
-      <c r="B53" s="21"/>
-      <c r="C53" s="21"/>
-      <c r="D53" s="21"/>
-      <c r="E53" s="21"/>
-      <c r="F53" s="21"/>
-      <c r="G53" s="21"/>
+      <c r="A53" s="20"/>
+      <c r="B53" s="20"/>
+      <c r="C53" s="20"/>
+      <c r="D53" s="20"/>
+      <c r="E53" s="20"/>
+      <c r="F53" s="20"/>
+      <c r="G53" s="20"/>
     </row>
     <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="21"/>
-      <c r="B54" s="21"/>
-      <c r="C54" s="21"/>
-      <c r="D54" s="21"/>
-      <c r="E54" s="21"/>
-      <c r="F54" s="21"/>
-      <c r="G54" s="21"/>
+      <c r="A54" s="20"/>
+      <c r="B54" s="20"/>
+      <c r="C54" s="20"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="20"/>
+      <c r="G54" s="20"/>
     </row>
     <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="21"/>
-      <c r="B55" s="21"/>
-      <c r="C55" s="21"/>
-      <c r="D55" s="21"/>
-      <c r="E55" s="21"/>
-      <c r="F55" s="21"/>
-      <c r="G55" s="21"/>
+      <c r="A55" s="20"/>
+      <c r="B55" s="20"/>
+      <c r="C55" s="20"/>
+      <c r="D55" s="20"/>
+      <c r="E55" s="20"/>
+      <c r="F55" s="20"/>
+      <c r="G55" s="20"/>
     </row>
     <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="21"/>
-      <c r="B56" s="21"/>
-      <c r="C56" s="21"/>
-      <c r="D56" s="21"/>
-      <c r="E56" s="21"/>
-      <c r="F56" s="21"/>
-      <c r="G56" s="21"/>
+      <c r="A56" s="20"/>
+      <c r="B56" s="20"/>
+      <c r="C56" s="20"/>
+      <c r="D56" s="20"/>
+      <c r="E56" s="20"/>
+      <c r="F56" s="20"/>
+      <c r="G56" s="20"/>
     </row>
     <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="21"/>
-      <c r="B57" s="21"/>
-      <c r="C57" s="21"/>
-      <c r="D57" s="21"/>
-      <c r="E57" s="21"/>
-      <c r="F57" s="21"/>
-      <c r="G57" s="21"/>
+      <c r="A57" s="20"/>
+      <c r="B57" s="20"/>
+      <c r="C57" s="20"/>
+      <c r="D57" s="20"/>
+      <c r="E57" s="20"/>
+      <c r="F57" s="20"/>
+      <c r="G57" s="20"/>
     </row>
     <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="21"/>
-      <c r="B58" s="21"/>
-      <c r="C58" s="21"/>
-      <c r="D58" s="21"/>
-      <c r="E58" s="21"/>
-      <c r="F58" s="21"/>
-      <c r="G58" s="21"/>
+      <c r="A58" s="20"/>
+      <c r="B58" s="20"/>
+      <c r="C58" s="20"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="20"/>
+      <c r="F58" s="20"/>
+      <c r="G58" s="20"/>
     </row>
     <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="21"/>
-      <c r="B59" s="21"/>
-      <c r="C59" s="21"/>
-      <c r="D59" s="21"/>
-      <c r="E59" s="21"/>
-      <c r="F59" s="21"/>
-      <c r="G59" s="21"/>
+      <c r="A59" s="20"/>
+      <c r="B59" s="20"/>
+      <c r="C59" s="20"/>
+      <c r="D59" s="20"/>
+      <c r="E59" s="20"/>
+      <c r="F59" s="20"/>
+      <c r="G59" s="20"/>
     </row>
     <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="21"/>
-      <c r="B60" s="21"/>
-      <c r="C60" s="21"/>
-      <c r="D60" s="21"/>
-      <c r="E60" s="21"/>
-      <c r="F60" s="21"/>
-      <c r="G60" s="21"/>
+      <c r="A60" s="20"/>
+      <c r="B60" s="20"/>
+      <c r="C60" s="20"/>
+      <c r="D60" s="20"/>
+      <c r="E60" s="20"/>
+      <c r="F60" s="20"/>
+      <c r="G60" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3649,154 +3665,154 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
+      <c r="A1" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
-        <v>223</v>
+      <c r="A3" s="21" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
-        <v>224</v>
-      </c>
-      <c r="B4" s="20" t="n">
+      <c r="A4" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="B4" s="19" t="n">
         <f aca="false">COUNTA('Test Scripts'!A3:A60)</f>
         <v>27</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
-        <v>225</v>
-      </c>
-      <c r="B5" s="20" t="n">
+      <c r="A5" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="B5" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!I3:I60,"Pass")</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="B6" s="20" t="n">
+      <c r="A6" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="B6" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!I3:I60,"Fail")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="B7" s="20" t="n">
+      <c r="A7" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="B7" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!I3:I60,"Blocked")</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="B8" s="20" t="n">
+      <c r="A8" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="B8" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!I3:I60,"In Progress")</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="B9" s="20" t="n">
+      <c r="A9" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="B9" s="19" t="n">
         <f aca="false">B4-B5-B6-B7-B8</f>
         <v>27</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
-        <v>230</v>
-      </c>
-      <c r="B10" s="23" t="n">
+      <c r="A10" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="B10" s="22" t="n">
         <f aca="false">IF((B5+B6)=0,0,B5/(B5+B6))</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="22" t="s">
-        <v>231</v>
+      <c r="A12" s="21" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="B13" s="20" t="n">
+      <c r="A13" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="B13" s="19" t="n">
         <f aca="false">COUNTIF('Test Scripts'!D3:D60,"Critical")-COUNTIFS('Test Scripts'!D3:D60,"Critical",'Test Scripts'!I3:I60,"Pass")</f>
         <v>9</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
-        <v>233</v>
-      </c>
-      <c r="B14" s="20" t="n">
+      <c r="A14" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="B14" s="19" t="n">
         <f aca="false">COUNTIFS('Defect Log'!$B$3:$B$60,"Critical",'Defect Log'!$C$3:$C$60,"Open")+COUNTIFS('Defect Log'!$B$3:$B$60,"Major",'Defect Log'!$C$3:$C$60,"Open")</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
-        <v>234</v>
-      </c>
-      <c r="B15" s="20" t="n">
+      <c r="A15" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="B15" s="19" t="n">
         <f aca="false">COUNTIF(Traceability!$D$3:$D$29,"N (GAP)")</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="24" t="s">
-        <v>235</v>
-      </c>
-      <c r="B16" s="25" t="str">
+      <c r="A16" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="B16" s="24" t="str">
         <f aca="false">IF(AND(B13=0,B14=0,B15=0),"READY for sign-off","NOT ready - blocked")</f>
         <v>NOT ready - blocked</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="22" t="s">
-        <v>236</v>
+      <c r="A18" s="21" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="B19" s="26"/>
+      <c r="A19" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="B19" s="25"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="B20" s="26"/>
+      <c r="A20" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="B20" s="25"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="B21" s="26"/>
+      <c r="A21" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="B21" s="25"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="B22" s="26"/>
+      <c r="A22" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="B22" s="25"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="27" t="s">
-        <v>241</v>
+      <c r="A24" s="26" t="s">
+        <v>243</v>
       </c>
     </row>
   </sheetData>
